--- a/v3/OG0049/OG0049_DevSpec.xlsx
+++ b/v3/OG0049/OG0049_DevSpec.xlsx
@@ -801,12 +801,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>What is Toby thinking?</t>
+          <t>What is Kira thinking?</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Think about what Toby wants to do now.</t>
+          <t>Think about what Kira learns about trash.</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SC03</t>
+          <t>SC04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>OG0049_SC03_I.webp</t>
+          <t>OG0049_SC04_I.webp</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>SC03</t>
+          <t>SC04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
@@ -1253,17 +1253,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>SC09</t>
+          <t>SC15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>OG0049_SC09_I.webp</t>
+          <t>OG0049_SC15_I.webp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>SC09</t>
+          <t>SC15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Kira and Toby</t>
+          <t>the Aurora submarine</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>deep in the ocean</t>
+          <t>into the dark canyon</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>see a tiny golden light</t>
+          <t>followed the light</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>submarine's</t>
+          <t>the submarine's</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>the</t>
+          <t>opened</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>opened</t>
+          <t>Toby</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Toby</t>
+          <t>Diver</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -1793,21 +1793,25 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>OG0049_V3_Q04</t>
+          <t>OG0049_V3_Q05</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Diver</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>afraid</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="F24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1818,21 +1822,25 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>afraid</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>해결 이후 감정을 위기 장면에 적용합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1842,23 +1850,23 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E26" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>해결 이후 감정을 위기 장면에 적용합니다.</t>
+          <t>위기감은 파악했지만 두려움과 분노를 혼동합니다.</t>
         </is>
       </c>
     </row>
@@ -1870,53 +1878,49 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>proud</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>위기감은 파악했지만 두려움과 분노를 혼동합니다.</t>
+          <t>구조 이후의 감정을 현재 장면에 투영합니다.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>OG0049_V3_Q05</t>
+          <t>OG0049_V3_Q06</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>proud</t>
+          <t>We should keep the ocean clean.</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E28" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>구조 이후의 감정을 현재 장면에 투영합니다.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1926,21 +1930,25 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>We must act now!</t>
+          <t>Plastic bags are not dangerous.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>이야기의 핵심 깨달음과 반대되는 생각을 선택합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1950,23 +1958,23 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>The light is not important.</t>
+          <t>One fish is not important.</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>중심 문제를 놓치고 반대되는 생각을 선택합니다.</t>
+          <t>인물의 책임감과 생명 보호 의도를 약하게 이해함</t>
         </is>
       </c>
     </row>
@@ -1978,51 +1986,23 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>The fish can fix it alone.</t>
+          <t>We should leave the trash in the sea.</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>도움이 필요한 상황과 인물의 의도를 연결하지 못합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>OG0049_V3_Q06</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>The cave is beautiful.</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>위험 단서를 배경 묘사로만 이해함</t>
+          <t>환경 보호 메시지와 반대되는 생각을 선택합니다.</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2252,7 +2232,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>kira_toby</t>
+          <t>aurora_submarine</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -2285,7 +2265,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>deep_ocean</t>
+          <t>dark_canyon</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -2318,7 +2298,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>see_light</t>
+          <t>followed_light</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -2541,7 +2521,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>the</t>
+          <t>the submarine's</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -2570,7 +2550,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>submarine's</t>
+          <t>silver</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -2599,7 +2579,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t>robot</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -2628,11 +2608,11 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>robot</t>
+          <t>arms.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -2652,29 +2632,29 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>OG0049_V3_Q04</t>
+          <t>OG0049_V3_Q05</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>arms.</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2.5</v>
+        <v>100</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>exact_position</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>8</v>
+          <t>option_score</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Actor/action/result word order.</t>
+          <t>Correct reaction/emotion.</t>
         </is>
       </c>
     </row>
@@ -2686,11 +2666,11 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -2698,12 +2678,12 @@
         </is>
       </c>
       <c r="E22" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Correct reaction/emotion.</t>
+          <t>해결 이후 감정을 위기 장면에 적용합니다.</t>
         </is>
       </c>
     </row>
@@ -2715,11 +2695,11 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -2732,7 +2712,7 @@
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>해결 이후 감정을 위기 장면에 적용합니다.</t>
+          <t>위기감은 파악했지만 두려움과 분노를 혼동합니다.</t>
         </is>
       </c>
     </row>
@@ -2744,11 +2724,11 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
@@ -2761,23 +2741,23 @@
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>위기감은 파악했지만 두려움과 분노를 혼동합니다.</t>
+          <t>구조 이후의 감정을 현재 장면에 투영합니다.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>OG0049_V3_Q05</t>
+          <t>OG0049_V3_Q06</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
@@ -2785,12 +2765,12 @@
         </is>
       </c>
       <c r="E25" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>구조 이후의 감정을 현재 장면에 투영합니다.</t>
+          <t>Correct internal response.</t>
         </is>
       </c>
     </row>
@@ -2802,11 +2782,11 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
@@ -2814,12 +2794,12 @@
         </is>
       </c>
       <c r="E26" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Correct internal response.</t>
+          <t>이야기의 핵심 깨달음과 반대되는 생각을 선택합니다.</t>
         </is>
       </c>
     </row>
@@ -2831,11 +2811,11 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
@@ -2848,7 +2828,7 @@
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>중심 문제를 놓치고 반대되는 생각을 선택합니다.</t>
+          <t>인물의 책임감과 생명 보호 의도를 약하게 이해함</t>
         </is>
       </c>
     </row>
@@ -2860,11 +2840,11 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
@@ -2877,36 +2857,7 @@
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>도움이 필요한 상황과 인물의 의도를 연결하지 못합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>OG0049_V3_Q06</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>option_score</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>위험 단서를 배경 묘사로만 이해함</t>
+          <t>환경 보호 메시지와 반대되는 생각을 선택합니다.</t>
         </is>
       </c>
     </row>
